--- a/Indicator_4/Real_data/Blue_Shark_SWPac.xlsx
+++ b/Indicator_4/Real_data/Blue_Shark_SWPac.xlsx
@@ -1,22 +1,300 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\EcoTest_Train\Indicator_4\Real_data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{089B86EC-A9F3-4D55-B116-B1838CE248C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="1" r:id="rId1"/>
     <sheet name="Time_series" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="89">
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Component</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Blue_Shark_SWPac</t>
+  </si>
+  <si>
+    <t>E.g. 'Swordfish_Natl'</t>
+  </si>
+  <si>
+    <t>Stock</t>
+  </si>
+  <si>
+    <t>max_age</t>
+  </si>
+  <si>
+    <t>14.979</t>
+  </si>
+  <si>
+    <t>Age to 5% natural survival</t>
+  </si>
+  <si>
+    <t>Life history</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>0.088</t>
+  </si>
+  <si>
+    <t>von Bertalannfy K</t>
+  </si>
+  <si>
+    <t>Linf</t>
+  </si>
+  <si>
+    <t>0.552</t>
+  </si>
+  <si>
+    <t>von Bertalannfy L-infinity (asymptotic length)</t>
+  </si>
+  <si>
+    <t>L50_Linf</t>
+  </si>
+  <si>
+    <t>326.07</t>
+  </si>
+  <si>
+    <t>Length at 50% maturity relative to asymptotic length (von B. L-infinity)</t>
+  </si>
+  <si>
+    <t>Total_L5_L50</t>
+  </si>
+  <si>
+    <t>0.366</t>
+  </si>
+  <si>
+    <t>Length at 5% selection relative to length at 50% maturity</t>
+  </si>
+  <si>
+    <t>Fleet selectivity</t>
+  </si>
+  <si>
+    <t>All fleets combined</t>
+  </si>
+  <si>
+    <t>Total_LFS_L50</t>
+  </si>
+  <si>
+    <t>1.051</t>
+  </si>
+  <si>
+    <t>Length at full selection relative to length at 50% maturity</t>
+  </si>
+  <si>
+    <t>Total_VML</t>
+  </si>
+  <si>
+    <t>0.333</t>
+  </si>
+  <si>
+    <t>Selectivity of maximum length class</t>
+  </si>
+  <si>
+    <t>Fleet_1_L5_L50</t>
+  </si>
+  <si>
+    <t>0.302</t>
+  </si>
+  <si>
+    <t>Fleet 1</t>
+  </si>
+  <si>
+    <t>Fleet_1_LFS_L50</t>
+  </si>
+  <si>
+    <t>0.541</t>
+  </si>
+  <si>
+    <t>Fleet_1_VML</t>
+  </si>
+  <si>
+    <t>0.474</t>
+  </si>
+  <si>
+    <t>Fleet_2_L5_L50</t>
+  </si>
+  <si>
+    <t>0.911</t>
+  </si>
+  <si>
+    <t>Fleet 2</t>
+  </si>
+  <si>
+    <t>Fleet_2_LFS_L50</t>
+  </si>
+  <si>
+    <t>1.064</t>
+  </si>
+  <si>
+    <t>Fleet_2_VML</t>
+  </si>
+  <si>
+    <t>0.025</t>
+  </si>
+  <si>
+    <t>Fleet_3_L5_L50</t>
+  </si>
+  <si>
+    <t>0.789</t>
+  </si>
+  <si>
+    <t>Fleet 3</t>
+  </si>
+  <si>
+    <t>Fleet_3_LFS_L50</t>
+  </si>
+  <si>
+    <t>1.091</t>
+  </si>
+  <si>
+    <t>Fleet_3_VML</t>
+  </si>
+  <si>
+    <t>0.239</t>
+  </si>
+  <si>
+    <t>Fleet_1_CF</t>
+  </si>
+  <si>
+    <t>0.084</t>
+  </si>
+  <si>
+    <t>Fraction of all historical catches that were Fleet 1</t>
+  </si>
+  <si>
+    <t>Fleet catch scale</t>
+  </si>
+  <si>
+    <t>Fleet_2_CF</t>
+  </si>
+  <si>
+    <t>0.802</t>
+  </si>
+  <si>
+    <t>Fraction of all historical catches that were Fleet 2</t>
+  </si>
+  <si>
+    <t>Fleet_3_CF</t>
+  </si>
+  <si>
+    <t>0.114</t>
+  </si>
+  <si>
+    <t>Fraction of all historical catches that were Fleet 3</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Total_catch</t>
+  </si>
+  <si>
+    <t>Total_mean_len</t>
+  </si>
+  <si>
+    <t>Total_mean_age</t>
+  </si>
+  <si>
+    <t>Total_CV_len</t>
+  </si>
+  <si>
+    <t>Total_frac_mat</t>
+  </si>
+  <si>
+    <t>Total_Index</t>
+  </si>
+  <si>
+    <t>Fleet_1_catch</t>
+  </si>
+  <si>
+    <t>Fleet_1_mean_len</t>
+  </si>
+  <si>
+    <t>Fleet_1_mean_age</t>
+  </si>
+  <si>
+    <t>Fleet_1_CV_len</t>
+  </si>
+  <si>
+    <t>Fleet_1_frac_mat</t>
+  </si>
+  <si>
+    <t>Fleet_1_Index</t>
+  </si>
+  <si>
+    <t>Fleet_2_catch</t>
+  </si>
+  <si>
+    <t>Fleet_2_mean_len</t>
+  </si>
+  <si>
+    <t>Fleet_2_mean_age</t>
+  </si>
+  <si>
+    <t>Fleet_2_CV_len</t>
+  </si>
+  <si>
+    <t>Fleet_2_frac_mat</t>
+  </si>
+  <si>
+    <t>Fleet_2_Index</t>
+  </si>
+  <si>
+    <t>Fleet_3_catch</t>
+  </si>
+  <si>
+    <t>Fleet_3_mean_len</t>
+  </si>
+  <si>
+    <t>Fleet_3_mean_age</t>
+  </si>
+  <si>
+    <t>Fleet_3_CV_len</t>
+  </si>
+  <si>
+    <t>Fleet_3_frac_mat</t>
+  </si>
+  <si>
+    <t>Fleet_3_Index</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -64,13 +342,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -108,7 +394,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -142,6 +428,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -176,9 +463,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -351,656 +639,368 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="31.36328125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Parameter</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Blue_Shark_SWPac</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Genus specius</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Billfish</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>North Atlantic</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>max_age</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>14.979</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Age to 5% natural survival</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Life history</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0.088</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>von Bertalannfy K</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Life history</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>L50_Linf</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0.552</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Length at 50% maturity relative to asymptotic length (von B. L-infinity)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Life history</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>All_L5_L50</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>0.366</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Length at 5% selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>All fleets combined</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>All_LFS_L50</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1.051</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Length at full selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>All fleets combined</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>All_VML</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>0.333</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Selectivity of maximum length class</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>All fleets combined</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Fleet_1_L5_L50</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>0.302</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Length at 5% selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Fleet 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Fleet_1_LFS_L50</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>0.541</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Length at full selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Fleet 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Fleet_1_VML</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>0.474</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Selectivity of maximum length class</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Fleet 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fleet_2_L5_L50</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>0.911</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Length at 5% selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Fleet 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Fleet_2_LFS_L50</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1.064</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Length at full selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Fleet 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fleet_2_VML</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>0.025</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Selectivity of maximum length class</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Fleet 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Fleet_3_L5_L50</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>0.789</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Length at 5% selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Fleet 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Fleet_3_LFS_L50</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1.091</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Length at full selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Fleet 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Fleet_3_VML</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>0.239</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Selectivity of maximum length class</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Fleet 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>All_ML_Linf</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.563</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Last historical mean length relative to Linf (e.g. mulen(2024) / Linf)</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Fleet catch-length</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>All fleets combined</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Fleet_1_ML_Linf</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.366</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Last historical mean length relative to Linf (e.g. mulen(2024) / Linf)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Fleet catch-length</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Fleet 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Fleet_2_ML_Linf</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Last historical mean length relative to Linf (e.g. mulen(2024) / Linf)</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Fleet catch-length</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Fleet 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Fleet_3_ML_Linf</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>0.563</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Last historical mean length relative to Linf (e.g. mulen(2024) / Linf)</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Fleet catch-length</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Fleet 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Fleet_1_CF</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>0.084</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Fraction of all historical catches that were Fleet 1</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Fleet catch scale</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Fleet 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Fleet_2_CF</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>0.802</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Fraction of all historical catches that were Fleet 2</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Fleet catch scale</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Fleet 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Fleet_3_CF</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>0.114</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Fraction of all historical catches that were Fleet 3</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Fleet catch scale</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Fleet 3</t>
-        </is>
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" t="s">
+        <v>57</v>
+      </c>
+      <c r="E20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1009,138 +1009,88 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Y27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Total_catch</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Total_mean_len</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Total_mean_age</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Total_CV_len</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Total_frac_mat</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Total_Index</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_catch</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_mean_len</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_mean_age</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_CV_len</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_frac_mat</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_Index</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_catch</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_mean_len</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_mean_age</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_CV_len</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_frac_mat</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_Index</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_catch</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_mean_len</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_mean_age</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_CV_len</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_frac_mat</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_Index</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1995</v>
       </c>
@@ -1148,108 +1098,108 @@
         <v>157.858</v>
       </c>
       <c r="C2">
-        <v>182.372</v>
+        <v>182.37200000000001</v>
       </c>
       <c r="E2">
-        <v>0.241</v>
+        <v>0.24099999999999999</v>
       </c>
       <c r="F2">
-        <v>0.549</v>
+        <v>0.54900000000000004</v>
       </c>
       <c r="G2">
-        <v>1.951</v>
+        <v>1.9510000000000001</v>
       </c>
       <c r="H2">
-        <v>88.697</v>
+        <v>88.697000000000003</v>
       </c>
       <c r="I2">
-        <v>140.754</v>
+        <v>140.75399999999999</v>
       </c>
       <c r="K2">
-        <v>0.387</v>
+        <v>0.38700000000000001</v>
       </c>
       <c r="L2">
-        <v>0.239</v>
+        <v>0.23899999999999999</v>
       </c>
       <c r="M2">
-        <v>0.416</v>
+        <v>0.41599999999999998</v>
       </c>
       <c r="O2">
-        <v>201.915</v>
+        <v>201.91499999999999</v>
       </c>
       <c r="Q2">
         <v>0.151</v>
       </c>
       <c r="R2">
-        <v>0.638</v>
+        <v>0.63800000000000001</v>
       </c>
       <c r="T2">
-        <v>69.161</v>
+        <v>69.161000000000001</v>
       </c>
       <c r="U2">
-        <v>204.449</v>
+        <v>204.44900000000001</v>
       </c>
       <c r="W2">
         <v>0.184</v>
       </c>
       <c r="X2">
-        <v>0.769</v>
+        <v>0.76900000000000002</v>
       </c>
       <c r="Y2">
         <v>1.288</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1996</v>
       </c>
       <c r="B3">
-        <v>305.453</v>
+        <v>305.45299999999997</v>
       </c>
       <c r="C3">
-        <v>170.183</v>
+        <v>170.18299999999999</v>
       </c>
       <c r="E3">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="F3">
-        <v>0.481</v>
+        <v>0.48099999999999998</v>
       </c>
       <c r="G3">
         <v>1.347</v>
       </c>
       <c r="H3">
-        <v>206.037</v>
+        <v>206.03700000000001</v>
       </c>
       <c r="I3">
-        <v>141.308</v>
+        <v>141.30799999999999</v>
       </c>
       <c r="K3">
-        <v>0.418</v>
+        <v>0.41799999999999998</v>
       </c>
       <c r="L3">
-        <v>0.262</v>
+        <v>0.26200000000000001</v>
       </c>
       <c r="M3">
-        <v>0.5649999999999999</v>
+        <v>0.56499999999999995</v>
       </c>
       <c r="T3">
-        <v>99.416</v>
+        <v>99.415999999999997</v>
       </c>
       <c r="U3">
-        <v>199.058</v>
+        <v>199.05799999999999</v>
       </c>
       <c r="W3">
-        <v>0.143</v>
+        <v>0.14299999999999999</v>
       </c>
       <c r="X3">
-        <v>0.701</v>
+        <v>0.70099999999999996</v>
       </c>
       <c r="Y3">
-        <v>1.312</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>1.3120000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1997</v>
       </c>
@@ -1257,10 +1207,10 @@
         <v>293</v>
       </c>
       <c r="C4">
-        <v>164.587</v>
+        <v>164.58699999999999</v>
       </c>
       <c r="E4">
-        <v>0.282</v>
+        <v>0.28199999999999997</v>
       </c>
       <c r="F4">
         <v>0.45</v>
@@ -1269,7 +1219,7 @@
         <v>1.347</v>
       </c>
       <c r="H4">
-        <v>161.533</v>
+        <v>161.53299999999999</v>
       </c>
       <c r="I4">
         <v>118.345</v>
@@ -1278,45 +1228,45 @@
         <v>0.4</v>
       </c>
       <c r="L4">
-        <v>0.095</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="M4">
-        <v>0.856</v>
+        <v>0.85599999999999998</v>
       </c>
       <c r="T4">
-        <v>131.467</v>
+        <v>131.46700000000001</v>
       </c>
       <c r="U4">
-        <v>210.829</v>
+        <v>210.82900000000001</v>
       </c>
       <c r="W4">
-        <v>0.165</v>
+        <v>0.16500000000000001</v>
       </c>
       <c r="X4">
-        <v>0.804</v>
+        <v>0.80400000000000005</v>
       </c>
       <c r="Y4">
         <v>1.601</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1998</v>
       </c>
       <c r="B5">
-        <v>367.966</v>
+        <v>367.96600000000001</v>
       </c>
       <c r="C5">
-        <v>160.606</v>
+        <v>160.60599999999999</v>
       </c>
       <c r="E5">
-        <v>0.213</v>
+        <v>0.21299999999999999</v>
       </c>
       <c r="F5">
         <v>0.193</v>
       </c>
       <c r="G5">
-        <v>1.362</v>
+        <v>1.3620000000000001</v>
       </c>
       <c r="H5">
         <v>208.423</v>
@@ -1328,28 +1278,28 @@
         <v>0.254</v>
       </c>
       <c r="L5">
-        <v>0.093</v>
+        <v>9.2999999999999999E-2</v>
       </c>
       <c r="M5">
-        <v>0.648</v>
+        <v>0.64800000000000002</v>
       </c>
       <c r="T5">
-        <v>159.543</v>
+        <v>159.54300000000001</v>
       </c>
       <c r="U5">
         <v>173.99</v>
       </c>
       <c r="W5">
-        <v>0.172</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="X5">
-        <v>0.292</v>
+        <v>0.29199999999999998</v>
       </c>
       <c r="Y5">
-        <v>1.273</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>1.2729999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1999</v>
       </c>
@@ -1357,54 +1307,54 @@
         <v>317.476</v>
       </c>
       <c r="C6">
-        <v>161.432</v>
+        <v>161.43199999999999</v>
       </c>
       <c r="E6">
-        <v>0.212</v>
+        <v>0.21199999999999999</v>
       </c>
       <c r="F6">
-        <v>0.231</v>
+        <v>0.23100000000000001</v>
       </c>
       <c r="G6">
-        <v>1.315</v>
+        <v>1.3149999999999999</v>
       </c>
       <c r="H6">
         <v>133.506</v>
       </c>
       <c r="I6">
-        <v>142.016</v>
+        <v>142.01599999999999</v>
       </c>
       <c r="K6">
-        <v>0.239</v>
+        <v>0.23899999999999999</v>
       </c>
       <c r="L6">
-        <v>0.063</v>
+        <v>6.3E-2</v>
       </c>
       <c r="M6">
-        <v>1.007</v>
+        <v>1.0069999999999999</v>
       </c>
       <c r="T6">
         <v>183.97</v>
       </c>
       <c r="U6">
-        <v>180.848</v>
+        <v>180.84800000000001</v>
       </c>
       <c r="W6">
         <v>0.185</v>
       </c>
       <c r="X6">
-        <v>0.399</v>
+        <v>0.39900000000000002</v>
       </c>
       <c r="Y6">
         <v>0.995</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2000</v>
       </c>
       <c r="B7">
-        <v>219.615</v>
+        <v>219.61500000000001</v>
       </c>
       <c r="C7">
         <v>157.256</v>
@@ -1419,22 +1369,22 @@
         <v>1.246</v>
       </c>
       <c r="H7">
-        <v>86.196</v>
+        <v>86.195999999999998</v>
       </c>
       <c r="I7">
-        <v>138.906</v>
+        <v>138.90600000000001</v>
       </c>
       <c r="K7">
-        <v>0.272</v>
+        <v>0.27200000000000002</v>
       </c>
       <c r="L7">
-        <v>0.079</v>
+        <v>7.9000000000000001E-2</v>
       </c>
       <c r="M7">
-        <v>1.011</v>
+        <v>1.0109999999999999</v>
       </c>
       <c r="T7">
-        <v>133.42</v>
+        <v>133.41999999999999</v>
       </c>
       <c r="U7">
         <v>175.607</v>
@@ -1443,27 +1393,27 @@
         <v>0.155</v>
       </c>
       <c r="X7">
-        <v>0.286</v>
+        <v>0.28599999999999998</v>
       </c>
       <c r="Y7">
         <v>1.276</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2001</v>
       </c>
       <c r="B8">
-        <v>272.155</v>
+        <v>272.15499999999997</v>
       </c>
       <c r="C8">
         <v>156.79</v>
       </c>
       <c r="E8">
-        <v>0.282</v>
+        <v>0.28199999999999997</v>
       </c>
       <c r="F8">
-        <v>0.236</v>
+        <v>0.23599999999999999</v>
       </c>
       <c r="G8">
         <v>1.137</v>
@@ -1475,45 +1425,45 @@
         <v>145.601</v>
       </c>
       <c r="K8">
-        <v>0.282</v>
+        <v>0.28199999999999997</v>
       </c>
       <c r="L8">
         <v>0.122</v>
       </c>
       <c r="M8">
-        <v>0.456</v>
+        <v>0.45600000000000002</v>
       </c>
       <c r="T8">
         <v>156.703</v>
       </c>
       <c r="U8">
-        <v>167.979</v>
+        <v>167.97900000000001</v>
       </c>
       <c r="W8">
-        <v>0.283</v>
+        <v>0.28299999999999997</v>
       </c>
       <c r="X8">
         <v>0.35</v>
       </c>
       <c r="Y8">
-        <v>1.001</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>1.0009999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2002</v>
       </c>
       <c r="B9">
-        <v>291.837</v>
+        <v>291.83699999999999</v>
       </c>
       <c r="C9">
-        <v>162.758</v>
+        <v>162.75800000000001</v>
       </c>
       <c r="E9">
         <v>0.245</v>
       </c>
       <c r="F9">
-        <v>0.286</v>
+        <v>0.28599999999999998</v>
       </c>
       <c r="G9">
         <v>1.03</v>
@@ -1525,7 +1475,7 @@
         <v>141.755</v>
       </c>
       <c r="K9">
-        <v>0.289</v>
+        <v>0.28899999999999998</v>
       </c>
       <c r="L9">
         <v>0.108</v>
@@ -1540,80 +1490,80 @@
         <v>183.761</v>
       </c>
       <c r="W9">
-        <v>0.201</v>
+        <v>0.20100000000000001</v>
       </c>
       <c r="X9">
-        <v>0.464</v>
+        <v>0.46400000000000002</v>
       </c>
       <c r="Y9">
         <v>1.171</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>2003</v>
       </c>
       <c r="B10">
-        <v>350.521</v>
+        <v>350.52100000000002</v>
       </c>
       <c r="C10">
         <v>182.458</v>
       </c>
       <c r="E10">
-        <v>0.203</v>
+        <v>0.20300000000000001</v>
       </c>
       <c r="F10">
-        <v>0.537</v>
+        <v>0.53700000000000003</v>
       </c>
       <c r="G10">
-        <v>0.989</v>
+        <v>0.98899999999999999</v>
       </c>
       <c r="H10">
-        <v>180.413</v>
+        <v>180.41300000000001</v>
       </c>
       <c r="I10">
-        <v>152.052</v>
+        <v>152.05199999999999</v>
       </c>
       <c r="K10">
-        <v>0.284</v>
+        <v>0.28399999999999997</v>
       </c>
       <c r="L10">
         <v>0.223</v>
       </c>
       <c r="M10">
-        <v>0.346</v>
+        <v>0.34599999999999997</v>
       </c>
       <c r="O10">
-        <v>211.116</v>
+        <v>211.11600000000001</v>
       </c>
       <c r="Q10">
-        <v>0.146</v>
+        <v>0.14599999999999999</v>
       </c>
       <c r="R10">
-        <v>0.852</v>
+        <v>0.85199999999999998</v>
       </c>
       <c r="T10">
         <v>170.108</v>
       </c>
       <c r="U10">
-        <v>184.206</v>
+        <v>184.20599999999999</v>
       </c>
       <c r="W10">
         <v>0.18</v>
       </c>
       <c r="X10">
-        <v>0.537</v>
+        <v>0.53700000000000003</v>
       </c>
       <c r="Y10">
-        <v>0.894</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>0.89400000000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>2004</v>
       </c>
       <c r="B11">
-        <v>705.578</v>
+        <v>705.57799999999997</v>
       </c>
       <c r="C11">
         <v>170.828</v>
@@ -1622,43 +1572,43 @@
         <v>0.182</v>
       </c>
       <c r="F11">
-        <v>0.427</v>
+        <v>0.42699999999999999</v>
       </c>
       <c r="G11">
-        <v>0.925</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="H11">
-        <v>187.668</v>
+        <v>187.66800000000001</v>
       </c>
       <c r="I11">
-        <v>129.507</v>
+        <v>129.50700000000001</v>
       </c>
       <c r="K11">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="L11">
-        <v>0.062</v>
+        <v>6.2E-2</v>
       </c>
       <c r="M11">
-        <v>0.517</v>
+        <v>0.51700000000000002</v>
       </c>
       <c r="N11">
-        <v>340.087</v>
+        <v>340.08699999999999</v>
       </c>
       <c r="O11">
         <v>188.333</v>
       </c>
       <c r="Q11">
-        <v>0.073</v>
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="R11">
-        <v>0.556</v>
+        <v>0.55600000000000005</v>
       </c>
       <c r="S11">
-        <v>0.589</v>
+        <v>0.58899999999999997</v>
       </c>
       <c r="T11">
-        <v>177.823</v>
+        <v>177.82300000000001</v>
       </c>
       <c r="U11">
         <v>194.643</v>
@@ -1667,13 +1617,13 @@
         <v>0.183</v>
       </c>
       <c r="X11">
-        <v>0.663</v>
+        <v>0.66300000000000003</v>
       </c>
       <c r="Y11">
-        <v>0.6850000000000001</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>0.68500000000000005</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2005</v>
       </c>
@@ -1681,43 +1631,43 @@
         <v>765.303</v>
       </c>
       <c r="C12">
-        <v>173.195</v>
+        <v>173.19499999999999</v>
       </c>
       <c r="E12">
-        <v>0.174</v>
+        <v>0.17399999999999999</v>
       </c>
       <c r="F12">
         <v>0.503</v>
       </c>
       <c r="G12">
-        <v>0.849</v>
+        <v>0.84899999999999998</v>
       </c>
       <c r="H12">
-        <v>93.02500000000001</v>
+        <v>93.025000000000006</v>
       </c>
       <c r="I12">
         <v>128.596</v>
       </c>
       <c r="K12">
-        <v>0.278</v>
+        <v>0.27800000000000002</v>
       </c>
       <c r="L12">
-        <v>0.042</v>
+        <v>4.2000000000000003E-2</v>
       </c>
       <c r="M12">
-        <v>0.657</v>
+        <v>0.65700000000000003</v>
       </c>
       <c r="N12">
-        <v>551.921</v>
+        <v>551.92100000000005</v>
       </c>
       <c r="O12">
-        <v>198.966</v>
+        <v>198.96600000000001</v>
       </c>
       <c r="Q12">
-        <v>0.083</v>
+        <v>8.3000000000000004E-2</v>
       </c>
       <c r="R12">
-        <v>0.828</v>
+        <v>0.82799999999999996</v>
       </c>
       <c r="S12">
         <v>0.51</v>
@@ -1732,13 +1682,13 @@
         <v>0.161</v>
       </c>
       <c r="X12">
-        <v>0.641</v>
+        <v>0.64100000000000001</v>
       </c>
       <c r="Y12">
-        <v>0.712</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>0.71199999999999997</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>2006</v>
       </c>
@@ -1746,55 +1696,55 @@
         <v>1489.942</v>
       </c>
       <c r="C13">
-        <v>158.936</v>
+        <v>158.93600000000001</v>
       </c>
       <c r="E13">
-        <v>0.197</v>
+        <v>0.19700000000000001</v>
       </c>
       <c r="F13">
-        <v>0.297</v>
+        <v>0.29699999999999999</v>
       </c>
       <c r="G13">
         <v>0.75</v>
       </c>
       <c r="H13">
-        <v>52.276</v>
+        <v>52.276000000000003</v>
       </c>
       <c r="I13">
         <v>129.673</v>
       </c>
       <c r="K13">
-        <v>0.242</v>
+        <v>0.24199999999999999</v>
       </c>
       <c r="L13">
         <v>0.04</v>
       </c>
       <c r="M13">
-        <v>0.722</v>
+        <v>0.72199999999999998</v>
       </c>
       <c r="N13">
         <v>1327.32</v>
       </c>
       <c r="S13">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="T13">
         <v>110.346</v>
       </c>
       <c r="U13">
-        <v>188.199</v>
+        <v>188.19900000000001</v>
       </c>
       <c r="W13">
         <v>0.152</v>
       </c>
       <c r="X13">
-        <v>0.555</v>
+        <v>0.55500000000000005</v>
       </c>
       <c r="Y13">
-        <v>0.658</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>0.65800000000000003</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>2007</v>
       </c>
@@ -1802,64 +1752,64 @@
         <v>3250.2</v>
       </c>
       <c r="C14">
-        <v>167.162</v>
+        <v>167.16200000000001</v>
       </c>
       <c r="E14">
-        <v>0.177</v>
+        <v>0.17699999999999999</v>
       </c>
       <c r="F14">
         <v>0.376</v>
       </c>
       <c r="G14">
-        <v>0.636</v>
+        <v>0.63600000000000001</v>
       </c>
       <c r="H14">
-        <v>42.075</v>
+        <v>42.075000000000003</v>
       </c>
       <c r="I14">
         <v>126.114</v>
       </c>
       <c r="K14">
-        <v>0.301</v>
+        <v>0.30099999999999999</v>
       </c>
       <c r="L14">
-        <v>0.053</v>
+        <v>5.2999999999999999E-2</v>
       </c>
       <c r="M14">
-        <v>0.901</v>
+        <v>0.90100000000000002</v>
       </c>
       <c r="N14">
         <v>3112.6</v>
       </c>
       <c r="O14">
-        <v>182.759</v>
+        <v>182.75899999999999</v>
       </c>
       <c r="Q14">
         <v>0.09</v>
       </c>
       <c r="R14">
-        <v>0.448</v>
+        <v>0.44800000000000001</v>
       </c>
       <c r="S14">
-        <v>0.479</v>
+        <v>0.47899999999999998</v>
       </c>
       <c r="T14">
-        <v>95.526</v>
+        <v>95.525999999999996</v>
       </c>
       <c r="U14">
         <v>192.613</v>
       </c>
       <c r="W14">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="X14">
         <v>0.626</v>
       </c>
       <c r="Y14">
-        <v>0.794</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>0.79400000000000004</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>2008</v>
       </c>
@@ -1867,60 +1817,60 @@
         <v>1837.23</v>
       </c>
       <c r="C15">
-        <v>158.693</v>
+        <v>158.69300000000001</v>
       </c>
       <c r="E15">
-        <v>0.237</v>
+        <v>0.23699999999999999</v>
       </c>
       <c r="F15">
         <v>0.376</v>
       </c>
       <c r="G15">
-        <v>0.595</v>
+        <v>0.59499999999999997</v>
       </c>
       <c r="H15">
-        <v>35.908</v>
+        <v>35.908000000000001</v>
       </c>
       <c r="I15">
         <v>125.514</v>
       </c>
       <c r="K15">
-        <v>0.324</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="L15">
         <v>0.111</v>
       </c>
       <c r="M15">
-        <v>1.128</v>
+        <v>1.1279999999999999</v>
       </c>
       <c r="N15">
         <v>1716.8</v>
       </c>
       <c r="S15">
-        <v>0.429</v>
+        <v>0.42899999999999999</v>
       </c>
       <c r="T15">
-        <v>84.52200000000001</v>
+        <v>84.522000000000006</v>
       </c>
       <c r="U15">
-        <v>191.873</v>
+        <v>191.87299999999999</v>
       </c>
       <c r="W15">
-        <v>0.149</v>
+        <v>0.14899999999999999</v>
       </c>
       <c r="X15">
-        <v>0.642</v>
+        <v>0.64200000000000002</v>
       </c>
       <c r="Y15">
-        <v>0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>0.69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>2009</v>
       </c>
       <c r="B16">
-        <v>1454.004</v>
+        <v>1454.0039999999999</v>
       </c>
       <c r="C16">
         <v>165.619</v>
@@ -1932,10 +1882,10 @@
         <v>0.378</v>
       </c>
       <c r="G16">
-        <v>0.575</v>
+        <v>0.57499999999999996</v>
       </c>
       <c r="H16">
-        <v>35.781</v>
+        <v>35.780999999999999</v>
       </c>
       <c r="I16">
         <v>139.739</v>
@@ -1944,7 +1894,7 @@
         <v>0.27</v>
       </c>
       <c r="L16">
-        <v>0.116</v>
+        <v>0.11600000000000001</v>
       </c>
       <c r="M16">
         <v>1.016</v>
@@ -1953,25 +1903,25 @@
         <v>1325.8</v>
       </c>
       <c r="S16">
-        <v>0.535</v>
+        <v>0.53500000000000003</v>
       </c>
       <c r="T16">
-        <v>92.423</v>
+        <v>92.423000000000002</v>
       </c>
       <c r="U16">
         <v>191.499</v>
       </c>
       <c r="W16">
-        <v>0.175</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="X16">
-        <v>0.639</v>
+        <v>0.63900000000000001</v>
       </c>
       <c r="Y16">
-        <v>0.5679999999999999</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>0.56799999999999995</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>2010</v>
       </c>
@@ -1982,22 +1932,22 @@
         <v>169.208</v>
       </c>
       <c r="E17">
-        <v>0.239</v>
+        <v>0.23899999999999999</v>
       </c>
       <c r="F17">
-        <v>0.418</v>
+        <v>0.41799999999999998</v>
       </c>
       <c r="G17">
-        <v>0.572</v>
+        <v>0.57199999999999995</v>
       </c>
       <c r="H17">
-        <v>36.563</v>
+        <v>36.563000000000002</v>
       </c>
       <c r="I17">
-        <v>136.793</v>
+        <v>136.79300000000001</v>
       </c>
       <c r="K17">
-        <v>0.292</v>
+        <v>0.29199999999999998</v>
       </c>
       <c r="L17">
         <v>0.11</v>
@@ -2009,25 +1959,25 @@
         <v>929.755</v>
       </c>
       <c r="S17">
-        <v>0.819</v>
+        <v>0.81899999999999995</v>
       </c>
       <c r="T17">
-        <v>117.796</v>
+        <v>117.79600000000001</v>
       </c>
       <c r="U17">
-        <v>201.623</v>
+        <v>201.62299999999999</v>
       </c>
       <c r="W17">
         <v>0.187</v>
       </c>
       <c r="X17">
-        <v>0.726</v>
+        <v>0.72599999999999998</v>
       </c>
       <c r="Y17">
-        <v>0.555</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>0.55500000000000005</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>2011</v>
       </c>
@@ -2038,10 +1988,10 @@
         <v>171.292</v>
       </c>
       <c r="E18">
-        <v>0.213</v>
+        <v>0.21299999999999999</v>
       </c>
       <c r="F18">
-        <v>0.392</v>
+        <v>0.39200000000000002</v>
       </c>
       <c r="G18">
         <v>0.622</v>
@@ -2056,7 +2006,7 @@
         <v>0.251</v>
       </c>
       <c r="L18">
-        <v>0.139</v>
+        <v>0.13900000000000001</v>
       </c>
       <c r="M18">
         <v>1.022</v>
@@ -2065,54 +2015,54 @@
         <v>1703.42</v>
       </c>
       <c r="S18">
-        <v>0.828</v>
+        <v>0.82799999999999996</v>
       </c>
       <c r="T18">
-        <v>99.44499999999999</v>
+        <v>99.444999999999993</v>
       </c>
       <c r="U18">
         <v>195.4</v>
       </c>
       <c r="W18">
-        <v>0.176</v>
+        <v>0.17599999999999999</v>
       </c>
       <c r="X18">
-        <v>0.645</v>
+        <v>0.64500000000000002</v>
       </c>
       <c r="Y18">
-        <v>0.826</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>0.82599999999999996</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>2012</v>
       </c>
       <c r="B19">
-        <v>2137.713</v>
+        <v>2137.7130000000002</v>
       </c>
       <c r="C19">
-        <v>158.973</v>
+        <v>158.97300000000001</v>
       </c>
       <c r="E19">
-        <v>0.204</v>
+        <v>0.20399999999999999</v>
       </c>
       <c r="F19">
-        <v>0.322</v>
+        <v>0.32200000000000001</v>
       </c>
       <c r="G19">
-        <v>0.6909999999999999</v>
+        <v>0.69099999999999995</v>
       </c>
       <c r="H19">
-        <v>55.633</v>
+        <v>55.633000000000003</v>
       </c>
       <c r="I19">
         <v>125.884</v>
       </c>
       <c r="K19">
-        <v>0.263</v>
+        <v>0.26300000000000001</v>
       </c>
       <c r="L19">
-        <v>0.037</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="M19">
         <v>1.544</v>
@@ -2127,57 +2077,57 @@
         <v>129.03</v>
       </c>
       <c r="U19">
-        <v>192.062</v>
+        <v>192.06200000000001</v>
       </c>
       <c r="W19">
-        <v>0.145</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="X19">
-        <v>0.607</v>
+        <v>0.60699999999999998</v>
       </c>
       <c r="Y19">
         <v>0.76</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>2013</v>
       </c>
       <c r="B20">
-        <v>1687.483</v>
+        <v>1687.4829999999999</v>
       </c>
       <c r="C20">
-        <v>155.575</v>
+        <v>155.57499999999999</v>
       </c>
       <c r="E20">
         <v>0.245</v>
       </c>
       <c r="F20">
-        <v>0.333</v>
+        <v>0.33300000000000002</v>
       </c>
       <c r="G20">
-        <v>0.757</v>
+        <v>0.75700000000000001</v>
       </c>
       <c r="H20">
-        <v>66.663</v>
+        <v>66.662999999999997</v>
       </c>
       <c r="I20">
-        <v>122.698</v>
+        <v>122.69799999999999</v>
       </c>
       <c r="K20">
-        <v>0.319</v>
+        <v>0.31900000000000001</v>
       </c>
       <c r="L20">
-        <v>0.074</v>
+        <v>7.3999999999999996E-2</v>
       </c>
       <c r="M20">
-        <v>1.628</v>
+        <v>1.6279999999999999</v>
       </c>
       <c r="N20">
         <v>1523.8</v>
       </c>
       <c r="S20">
-        <v>1.068</v>
+        <v>1.0680000000000001</v>
       </c>
       <c r="T20">
         <v>97.02</v>
@@ -2186,16 +2136,16 @@
         <v>188.452</v>
       </c>
       <c r="W20">
-        <v>0.171</v>
+        <v>0.17100000000000001</v>
       </c>
       <c r="X20">
-        <v>0.593</v>
+        <v>0.59299999999999997</v>
       </c>
       <c r="Y20">
         <v>0.76</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>2014</v>
       </c>
@@ -2203,7 +2153,7 @@
         <v>1573.498</v>
       </c>
       <c r="C21">
-        <v>159.908</v>
+        <v>159.90799999999999</v>
       </c>
       <c r="E21">
         <v>0.217</v>
@@ -2212,19 +2162,19 @@
         <v>0.318</v>
       </c>
       <c r="G21">
-        <v>0.831</v>
+        <v>0.83099999999999996</v>
       </c>
       <c r="H21">
-        <v>58.379</v>
+        <v>58.378999999999998</v>
       </c>
       <c r="I21">
-        <v>132.502</v>
+        <v>132.50200000000001</v>
       </c>
       <c r="K21">
-        <v>0.274</v>
+        <v>0.27400000000000002</v>
       </c>
       <c r="L21">
-        <v>0.042</v>
+        <v>4.2000000000000003E-2</v>
       </c>
       <c r="M21">
         <v>1.861</v>
@@ -2233,45 +2183,45 @@
         <v>1418.8</v>
       </c>
       <c r="S21">
-        <v>1.372</v>
+        <v>1.3720000000000001</v>
       </c>
       <c r="T21">
-        <v>96.319</v>
+        <v>96.319000000000003</v>
       </c>
       <c r="U21">
-        <v>187.313</v>
+        <v>187.31299999999999</v>
       </c>
       <c r="W21">
         <v>0.159</v>
       </c>
       <c r="X21">
-        <v>0.595</v>
+        <v>0.59499999999999997</v>
       </c>
       <c r="Y21">
-        <v>1.192</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>1.1919999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2015</v>
       </c>
       <c r="B22">
-        <v>912.222</v>
+        <v>912.22199999999998</v>
       </c>
       <c r="C22">
-        <v>150.288</v>
+        <v>150.28800000000001</v>
       </c>
       <c r="E22">
-        <v>0.233</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="F22">
         <v>0.311</v>
       </c>
       <c r="G22">
-        <v>0.867</v>
+        <v>0.86699999999999999</v>
       </c>
       <c r="H22">
-        <v>42.084</v>
+        <v>42.084000000000003</v>
       </c>
       <c r="I22">
         <v>112.575</v>
@@ -2280,48 +2230,48 @@
         <v>0.32</v>
       </c>
       <c r="L22">
-        <v>0.038</v>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="M22">
-        <v>1.945</v>
+        <v>1.9450000000000001</v>
       </c>
       <c r="N22">
-        <v>788.8049999999999</v>
+        <v>788.80499999999995</v>
       </c>
       <c r="T22">
-        <v>81.333</v>
+        <v>81.332999999999998</v>
       </c>
       <c r="U22">
         <v>188.001</v>
       </c>
       <c r="W22">
-        <v>0.147</v>
+        <v>0.14699999999999999</v>
       </c>
       <c r="X22">
-        <v>0.584</v>
+        <v>0.58399999999999996</v>
       </c>
       <c r="Y22">
-        <v>1.098</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>1.0980000000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>2016</v>
       </c>
       <c r="B23">
-        <v>599.789</v>
+        <v>599.78899999999999</v>
       </c>
       <c r="C23">
-        <v>157.342</v>
+        <v>157.34200000000001</v>
       </c>
       <c r="E23">
-        <v>0.233</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="F23">
         <v>0.34</v>
       </c>
       <c r="G23">
-        <v>0.922</v>
+        <v>0.92200000000000004</v>
       </c>
       <c r="H23">
         <v>25.93</v>
@@ -2333,10 +2283,10 @@
         <v>0.31</v>
       </c>
       <c r="L23">
-        <v>0.092</v>
+        <v>9.1999999999999998E-2</v>
       </c>
       <c r="M23">
-        <v>1.362</v>
+        <v>1.3620000000000001</v>
       </c>
       <c r="N23">
         <v>502.51</v>
@@ -2345,22 +2295,22 @@
         <v>1.177</v>
       </c>
       <c r="T23">
-        <v>71.34999999999999</v>
+        <v>71.349999999999994</v>
       </c>
       <c r="U23">
-        <v>189.039</v>
+        <v>189.03899999999999</v>
       </c>
       <c r="W23">
         <v>0.155</v>
       </c>
       <c r="X23">
-        <v>0.588</v>
+        <v>0.58799999999999997</v>
       </c>
       <c r="Y23">
         <v>1.175</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>2017</v>
       </c>
@@ -2368,63 +2318,63 @@
         <v>1088.893</v>
       </c>
       <c r="C24">
-        <v>142.908</v>
+        <v>142.90799999999999</v>
       </c>
       <c r="E24">
         <v>0.218</v>
       </c>
       <c r="F24">
-        <v>0.289</v>
+        <v>0.28899999999999998</v>
       </c>
       <c r="G24">
-        <v>0.982</v>
+        <v>0.98199999999999998</v>
       </c>
       <c r="H24">
         <v>30.276</v>
       </c>
       <c r="I24">
-        <v>98.39100000000001</v>
+        <v>98.391000000000005</v>
       </c>
       <c r="K24">
-        <v>0.296</v>
+        <v>0.29599999999999999</v>
       </c>
       <c r="L24">
-        <v>0.008</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="M24">
-        <v>1.176</v>
+        <v>1.1759999999999999</v>
       </c>
       <c r="N24">
-        <v>983.8819999999999</v>
+        <v>983.88199999999995</v>
       </c>
       <c r="S24">
         <v>1.526</v>
       </c>
       <c r="T24">
-        <v>74.735</v>
+        <v>74.734999999999999</v>
       </c>
       <c r="U24">
-        <v>187.424</v>
+        <v>187.42400000000001</v>
       </c>
       <c r="W24">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="X24">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="Y24">
-        <v>1.309</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>1.3089999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>2018</v>
       </c>
       <c r="B25">
-        <v>1373.661</v>
+        <v>1373.6610000000001</v>
       </c>
       <c r="C25">
-        <v>140.944</v>
+        <v>140.94399999999999</v>
       </c>
       <c r="E25">
         <v>0.307</v>
@@ -2436,48 +2386,48 @@
         <v>1.087</v>
       </c>
       <c r="H25">
-        <v>42.967</v>
+        <v>42.966999999999999</v>
       </c>
       <c r="I25">
-        <v>98.51900000000001</v>
+        <v>98.519000000000005</v>
       </c>
       <c r="K25">
-        <v>0.469</v>
+        <v>0.46899999999999997</v>
       </c>
       <c r="L25">
-        <v>0.08799999999999999</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="M25">
-        <v>1.422</v>
+        <v>1.4219999999999999</v>
       </c>
       <c r="N25">
         <v>1255.27</v>
       </c>
       <c r="S25">
-        <v>2.388</v>
+        <v>2.3879999999999999</v>
       </c>
       <c r="T25">
-        <v>75.425</v>
+        <v>75.424999999999997</v>
       </c>
       <c r="U25">
-        <v>183.368</v>
+        <v>183.36799999999999</v>
       </c>
       <c r="W25">
-        <v>0.144</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="X25">
-        <v>0.525</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="Y25">
-        <v>1.249</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>1.2490000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>2019</v>
       </c>
       <c r="B26">
-        <v>1521.121</v>
+        <v>1521.1210000000001</v>
       </c>
       <c r="C26">
         <v>156.03</v>
@@ -2486,7 +2436,7 @@
         <v>0.25</v>
       </c>
       <c r="F26">
-        <v>0.383</v>
+        <v>0.38300000000000001</v>
       </c>
       <c r="G26">
         <v>1.234</v>
@@ -2498,10 +2448,10 @@
         <v>119.379</v>
       </c>
       <c r="K26">
-        <v>0.366</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="L26">
-        <v>0.08599999999999999</v>
+        <v>8.5999999999999993E-2</v>
       </c>
       <c r="M26">
         <v>1.401</v>
@@ -2510,16 +2460,16 @@
         <v>1422.63</v>
       </c>
       <c r="S26">
-        <v>1.626</v>
+        <v>1.6259999999999999</v>
       </c>
       <c r="T26">
-        <v>88.036</v>
+        <v>88.036000000000001</v>
       </c>
       <c r="U26">
-        <v>192.681</v>
+        <v>192.68100000000001</v>
       </c>
       <c r="W26">
-        <v>0.134</v>
+        <v>0.13400000000000001</v>
       </c>
       <c r="X26">
         <v>0.68</v>
@@ -2528,21 +2478,21 @@
         <v>1.159</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2020</v>
       </c>
       <c r="B27">
-        <v>95.995</v>
+        <v>95.995000000000005</v>
       </c>
       <c r="C27">
-        <v>183.591</v>
+        <v>183.59100000000001</v>
       </c>
       <c r="E27">
         <v>0.13</v>
       </c>
       <c r="F27">
-        <v>0.615</v>
+        <v>0.61499999999999999</v>
       </c>
       <c r="G27">
         <v>1.38</v>
@@ -2551,16 +2501,16 @@
         <v>22.83</v>
       </c>
       <c r="T27">
-        <v>73.16500000000001</v>
+        <v>73.165000000000006</v>
       </c>
       <c r="U27">
-        <v>183.591</v>
+        <v>183.59100000000001</v>
       </c>
       <c r="W27">
         <v>0.13</v>
       </c>
       <c r="X27">
-        <v>0.615</v>
+        <v>0.61499999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/Indicator_4/Real_data/Blue_Shark_SWPac.xlsx
+++ b/Indicator_4/Real_data/Blue_Shark_SWPac.xlsx
@@ -1,300 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\EcoTest_Train\Indicator_4\Real_data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{089B86EC-A9F3-4D55-B116-B1838CE248C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="1" r:id="rId1"/>
     <sheet name="Time_series" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="89">
-  <si>
-    <t>Parameter</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Component</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Blue_Shark_SWPac</t>
-  </si>
-  <si>
-    <t>E.g. 'Swordfish_Natl'</t>
-  </si>
-  <si>
-    <t>Stock</t>
-  </si>
-  <si>
-    <t>max_age</t>
-  </si>
-  <si>
-    <t>14.979</t>
-  </si>
-  <si>
-    <t>Age to 5% natural survival</t>
-  </si>
-  <si>
-    <t>Life history</t>
-  </si>
-  <si>
-    <t>K</t>
-  </si>
-  <si>
-    <t>0.088</t>
-  </si>
-  <si>
-    <t>von Bertalannfy K</t>
-  </si>
-  <si>
-    <t>Linf</t>
-  </si>
-  <si>
-    <t>0.552</t>
-  </si>
-  <si>
-    <t>von Bertalannfy L-infinity (asymptotic length)</t>
-  </si>
-  <si>
-    <t>L50_Linf</t>
-  </si>
-  <si>
-    <t>326.07</t>
-  </si>
-  <si>
-    <t>Length at 50% maturity relative to asymptotic length (von B. L-infinity)</t>
-  </si>
-  <si>
-    <t>Total_L5_L50</t>
-  </si>
-  <si>
-    <t>0.366</t>
-  </si>
-  <si>
-    <t>Length at 5% selection relative to length at 50% maturity</t>
-  </si>
-  <si>
-    <t>Fleet selectivity</t>
-  </si>
-  <si>
-    <t>All fleets combined</t>
-  </si>
-  <si>
-    <t>Total_LFS_L50</t>
-  </si>
-  <si>
-    <t>1.051</t>
-  </si>
-  <si>
-    <t>Length at full selection relative to length at 50% maturity</t>
-  </si>
-  <si>
-    <t>Total_VML</t>
-  </si>
-  <si>
-    <t>0.333</t>
-  </si>
-  <si>
-    <t>Selectivity of maximum length class</t>
-  </si>
-  <si>
-    <t>Fleet_1_L5_L50</t>
-  </si>
-  <si>
-    <t>0.302</t>
-  </si>
-  <si>
-    <t>Fleet 1</t>
-  </si>
-  <si>
-    <t>Fleet_1_LFS_L50</t>
-  </si>
-  <si>
-    <t>0.541</t>
-  </si>
-  <si>
-    <t>Fleet_1_VML</t>
-  </si>
-  <si>
-    <t>0.474</t>
-  </si>
-  <si>
-    <t>Fleet_2_L5_L50</t>
-  </si>
-  <si>
-    <t>0.911</t>
-  </si>
-  <si>
-    <t>Fleet 2</t>
-  </si>
-  <si>
-    <t>Fleet_2_LFS_L50</t>
-  </si>
-  <si>
-    <t>1.064</t>
-  </si>
-  <si>
-    <t>Fleet_2_VML</t>
-  </si>
-  <si>
-    <t>0.025</t>
-  </si>
-  <si>
-    <t>Fleet_3_L5_L50</t>
-  </si>
-  <si>
-    <t>0.789</t>
-  </si>
-  <si>
-    <t>Fleet 3</t>
-  </si>
-  <si>
-    <t>Fleet_3_LFS_L50</t>
-  </si>
-  <si>
-    <t>1.091</t>
-  </si>
-  <si>
-    <t>Fleet_3_VML</t>
-  </si>
-  <si>
-    <t>0.239</t>
-  </si>
-  <si>
-    <t>Fleet_1_CF</t>
-  </si>
-  <si>
-    <t>0.084</t>
-  </si>
-  <si>
-    <t>Fraction of all historical catches that were Fleet 1</t>
-  </si>
-  <si>
-    <t>Fleet catch scale</t>
-  </si>
-  <si>
-    <t>Fleet_2_CF</t>
-  </si>
-  <si>
-    <t>0.802</t>
-  </si>
-  <si>
-    <t>Fraction of all historical catches that were Fleet 2</t>
-  </si>
-  <si>
-    <t>Fleet_3_CF</t>
-  </si>
-  <si>
-    <t>0.114</t>
-  </si>
-  <si>
-    <t>Fraction of all historical catches that were Fleet 3</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>Total_catch</t>
-  </si>
-  <si>
-    <t>Total_mean_len</t>
-  </si>
-  <si>
-    <t>Total_mean_age</t>
-  </si>
-  <si>
-    <t>Total_CV_len</t>
-  </si>
-  <si>
-    <t>Total_frac_mat</t>
-  </si>
-  <si>
-    <t>Total_Index</t>
-  </si>
-  <si>
-    <t>Fleet_1_catch</t>
-  </si>
-  <si>
-    <t>Fleet_1_mean_len</t>
-  </si>
-  <si>
-    <t>Fleet_1_mean_age</t>
-  </si>
-  <si>
-    <t>Fleet_1_CV_len</t>
-  </si>
-  <si>
-    <t>Fleet_1_frac_mat</t>
-  </si>
-  <si>
-    <t>Fleet_1_Index</t>
-  </si>
-  <si>
-    <t>Fleet_2_catch</t>
-  </si>
-  <si>
-    <t>Fleet_2_mean_len</t>
-  </si>
-  <si>
-    <t>Fleet_2_mean_age</t>
-  </si>
-  <si>
-    <t>Fleet_2_CV_len</t>
-  </si>
-  <si>
-    <t>Fleet_2_frac_mat</t>
-  </si>
-  <si>
-    <t>Fleet_2_Index</t>
-  </si>
-  <si>
-    <t>Fleet_3_catch</t>
-  </si>
-  <si>
-    <t>Fleet_3_mean_len</t>
-  </si>
-  <si>
-    <t>Fleet_3_mean_age</t>
-  </si>
-  <si>
-    <t>Fleet_3_CV_len</t>
-  </si>
-  <si>
-    <t>Fleet_3_frac_mat</t>
-  </si>
-  <si>
-    <t>Fleet_3_Index</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -342,21 +64,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -394,7 +108,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -428,7 +142,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -463,10 +176,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -639,368 +351,575 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="31.36328125" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" t="s">
-        <v>57</v>
-      </c>
-      <c r="E19" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>58</v>
-      </c>
-      <c r="B20" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" t="s">
-        <v>57</v>
-      </c>
-      <c r="E20" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>61</v>
-      </c>
-      <c r="B21" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" t="s">
-        <v>63</v>
-      </c>
-      <c r="D21" t="s">
-        <v>57</v>
-      </c>
-      <c r="E21" t="s">
-        <v>49</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Blue_Shark_SWPac</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>E.g. 'Swordfish_Natl'</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>max_age</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>14.979</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Age to 5% natural survival</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Life history</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0.088</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>von Bertalannfy K</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Life history</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Linf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.552</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>von Bertalannfy L-infinity (asymptotic length)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Life history</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>L50_Linf</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>326.07</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Length at 50% maturity relative to asymptotic length (von B. L-infinity)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Life history</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Total_L5_L50</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0.366</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Length at 5% selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>All fleets combined</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Total_LFS_L50</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1.051</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Length at full selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>All fleets combined</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Total_VML</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Selectivity of maximum length class</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>All fleets combined</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Fleet_1_L5_L50</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0.302</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Length at 5% selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Fleet 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Fleet_1_LFS_L50</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.541</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Length at full selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Fleet 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Fleet_1_VML</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.474</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Selectivity of maximum length class</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Fleet 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Fleet_2_L5_L50</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0.911</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Length at 5% selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Fleet 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Fleet_2_LFS_L50</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.064</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Length at full selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Fleet 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Fleet_2_VML</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0.025</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Selectivity of maximum length class</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Fleet 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fleet_3_L5_L50</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0.789</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Length at 5% selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Fleet 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Fleet_3_LFS_L50</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.091</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Length at full selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Fleet 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Fleet_3_VML</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.239</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Selectivity of maximum length class</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Fleet 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fleet_1_CF</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.084</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Fraction of all historical catches that were Fleet 1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Fleet catch scale</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Fleet 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fleet_2_CF</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.802</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Fraction of all historical catches that were Fleet 2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Fleet catch scale</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Fleet 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Fleet_3_CF</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0.114</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Fraction of all historical catches that were Fleet 3</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Fleet catch scale</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Fleet 3</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1009,88 +928,138 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Y27"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Total_catch</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Total_mean_len</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Total_mean_age</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Total_CV_len</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Total_frac_mat</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Total_Index</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_catch</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_mean_len</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_mean_age</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_CV_len</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_frac_mat</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_Index</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_catch</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_mean_len</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_mean_age</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_CV_len</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_frac_mat</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_Index</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_catch</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_mean_len</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_mean_age</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_CV_len</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_frac_mat</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_Index</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
         <v>1995</v>
       </c>
@@ -1098,108 +1067,108 @@
         <v>157.858</v>
       </c>
       <c r="C2">
-        <v>182.37200000000001</v>
+        <v>182.372</v>
       </c>
       <c r="E2">
-        <v>0.24099999999999999</v>
+        <v>0.241</v>
       </c>
       <c r="F2">
-        <v>0.54900000000000004</v>
+        <v>0.549</v>
       </c>
       <c r="G2">
-        <v>1.9510000000000001</v>
+        <v>1.951</v>
       </c>
       <c r="H2">
-        <v>88.697000000000003</v>
+        <v>88.697</v>
       </c>
       <c r="I2">
-        <v>140.75399999999999</v>
+        <v>140.754</v>
       </c>
       <c r="K2">
-        <v>0.38700000000000001</v>
+        <v>0.387</v>
       </c>
       <c r="L2">
-        <v>0.23899999999999999</v>
+        <v>0.239</v>
       </c>
       <c r="M2">
-        <v>0.41599999999999998</v>
+        <v>0.416</v>
       </c>
       <c r="O2">
-        <v>201.91499999999999</v>
+        <v>201.915</v>
       </c>
       <c r="Q2">
         <v>0.151</v>
       </c>
       <c r="R2">
-        <v>0.63800000000000001</v>
+        <v>0.638</v>
       </c>
       <c r="T2">
-        <v>69.161000000000001</v>
+        <v>69.161</v>
       </c>
       <c r="U2">
-        <v>204.44900000000001</v>
+        <v>204.449</v>
       </c>
       <c r="W2">
         <v>0.184</v>
       </c>
       <c r="X2">
-        <v>0.76900000000000002</v>
+        <v>0.769</v>
       </c>
       <c r="Y2">
         <v>1.288</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="3">
       <c r="A3">
         <v>1996</v>
       </c>
       <c r="B3">
-        <v>305.45299999999997</v>
+        <v>305.453</v>
       </c>
       <c r="C3">
-        <v>170.18299999999999</v>
+        <v>170.183</v>
       </c>
       <c r="E3">
-        <v>0.28000000000000003</v>
+        <v>0.28</v>
       </c>
       <c r="F3">
-        <v>0.48099999999999998</v>
+        <v>0.481</v>
       </c>
       <c r="G3">
         <v>1.347</v>
       </c>
       <c r="H3">
-        <v>206.03700000000001</v>
+        <v>206.037</v>
       </c>
       <c r="I3">
-        <v>141.30799999999999</v>
+        <v>141.308</v>
       </c>
       <c r="K3">
-        <v>0.41799999999999998</v>
+        <v>0.418</v>
       </c>
       <c r="L3">
-        <v>0.26200000000000001</v>
+        <v>0.262</v>
       </c>
       <c r="M3">
-        <v>0.56499999999999995</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="T3">
-        <v>99.415999999999997</v>
+        <v>99.416</v>
       </c>
       <c r="U3">
-        <v>199.05799999999999</v>
+        <v>199.058</v>
       </c>
       <c r="W3">
-        <v>0.14299999999999999</v>
+        <v>0.143</v>
       </c>
       <c r="X3">
-        <v>0.70099999999999996</v>
+        <v>0.701</v>
       </c>
       <c r="Y3">
-        <v>1.3120000000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.312</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4">
         <v>1997</v>
       </c>
@@ -1207,10 +1176,10 @@
         <v>293</v>
       </c>
       <c r="C4">
-        <v>164.58699999999999</v>
+        <v>164.587</v>
       </c>
       <c r="E4">
-        <v>0.28199999999999997</v>
+        <v>0.282</v>
       </c>
       <c r="F4">
         <v>0.45</v>
@@ -1219,7 +1188,7 @@
         <v>1.347</v>
       </c>
       <c r="H4">
-        <v>161.53299999999999</v>
+        <v>161.533</v>
       </c>
       <c r="I4">
         <v>118.345</v>
@@ -1228,45 +1197,45 @@
         <v>0.4</v>
       </c>
       <c r="L4">
-        <v>9.5000000000000001E-2</v>
+        <v>0.095</v>
       </c>
       <c r="M4">
-        <v>0.85599999999999998</v>
+        <v>0.856</v>
       </c>
       <c r="T4">
-        <v>131.46700000000001</v>
+        <v>131.467</v>
       </c>
       <c r="U4">
-        <v>210.82900000000001</v>
+        <v>210.829</v>
       </c>
       <c r="W4">
-        <v>0.16500000000000001</v>
+        <v>0.165</v>
       </c>
       <c r="X4">
-        <v>0.80400000000000005</v>
+        <v>0.804</v>
       </c>
       <c r="Y4">
         <v>1.601</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="5">
       <c r="A5">
         <v>1998</v>
       </c>
       <c r="B5">
-        <v>367.96600000000001</v>
+        <v>367.966</v>
       </c>
       <c r="C5">
-        <v>160.60599999999999</v>
+        <v>160.606</v>
       </c>
       <c r="E5">
-        <v>0.21299999999999999</v>
+        <v>0.213</v>
       </c>
       <c r="F5">
         <v>0.193</v>
       </c>
       <c r="G5">
-        <v>1.3620000000000001</v>
+        <v>1.362</v>
       </c>
       <c r="H5">
         <v>208.423</v>
@@ -1278,28 +1247,28 @@
         <v>0.254</v>
       </c>
       <c r="L5">
-        <v>9.2999999999999999E-2</v>
+        <v>0.093</v>
       </c>
       <c r="M5">
-        <v>0.64800000000000002</v>
+        <v>0.648</v>
       </c>
       <c r="T5">
-        <v>159.54300000000001</v>
+        <v>159.543</v>
       </c>
       <c r="U5">
         <v>173.99</v>
       </c>
       <c r="W5">
-        <v>0.17199999999999999</v>
+        <v>0.172</v>
       </c>
       <c r="X5">
-        <v>0.29199999999999998</v>
+        <v>0.292</v>
       </c>
       <c r="Y5">
-        <v>1.2729999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.273</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6">
         <v>1999</v>
       </c>
@@ -1307,54 +1276,54 @@
         <v>317.476</v>
       </c>
       <c r="C6">
-        <v>161.43199999999999</v>
+        <v>161.432</v>
       </c>
       <c r="E6">
-        <v>0.21199999999999999</v>
+        <v>0.212</v>
       </c>
       <c r="F6">
-        <v>0.23100000000000001</v>
+        <v>0.231</v>
       </c>
       <c r="G6">
-        <v>1.3149999999999999</v>
+        <v>1.315</v>
       </c>
       <c r="H6">
         <v>133.506</v>
       </c>
       <c r="I6">
-        <v>142.01599999999999</v>
+        <v>142.016</v>
       </c>
       <c r="K6">
-        <v>0.23899999999999999</v>
+        <v>0.239</v>
       </c>
       <c r="L6">
-        <v>6.3E-2</v>
+        <v>0.063</v>
       </c>
       <c r="M6">
-        <v>1.0069999999999999</v>
+        <v>1.007</v>
       </c>
       <c r="T6">
         <v>183.97</v>
       </c>
       <c r="U6">
-        <v>180.84800000000001</v>
+        <v>180.848</v>
       </c>
       <c r="W6">
         <v>0.185</v>
       </c>
       <c r="X6">
-        <v>0.39900000000000002</v>
+        <v>0.399</v>
       </c>
       <c r="Y6">
         <v>0.995</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7">
         <v>2000</v>
       </c>
       <c r="B7">
-        <v>219.61500000000001</v>
+        <v>219.615</v>
       </c>
       <c r="C7">
         <v>157.256</v>
@@ -1369,22 +1338,22 @@
         <v>1.246</v>
       </c>
       <c r="H7">
-        <v>86.195999999999998</v>
+        <v>86.196</v>
       </c>
       <c r="I7">
-        <v>138.90600000000001</v>
+        <v>138.906</v>
       </c>
       <c r="K7">
-        <v>0.27200000000000002</v>
+        <v>0.272</v>
       </c>
       <c r="L7">
-        <v>7.9000000000000001E-2</v>
+        <v>0.079</v>
       </c>
       <c r="M7">
-        <v>1.0109999999999999</v>
+        <v>1.011</v>
       </c>
       <c r="T7">
-        <v>133.41999999999999</v>
+        <v>133.42</v>
       </c>
       <c r="U7">
         <v>175.607</v>
@@ -1393,27 +1362,27 @@
         <v>0.155</v>
       </c>
       <c r="X7">
-        <v>0.28599999999999998</v>
+        <v>0.286</v>
       </c>
       <c r="Y7">
         <v>1.276</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8">
         <v>2001</v>
       </c>
       <c r="B8">
-        <v>272.15499999999997</v>
+        <v>272.155</v>
       </c>
       <c r="C8">
         <v>156.79</v>
       </c>
       <c r="E8">
-        <v>0.28199999999999997</v>
+        <v>0.282</v>
       </c>
       <c r="F8">
-        <v>0.23599999999999999</v>
+        <v>0.236</v>
       </c>
       <c r="G8">
         <v>1.137</v>
@@ -1425,45 +1394,45 @@
         <v>145.601</v>
       </c>
       <c r="K8">
-        <v>0.28199999999999997</v>
+        <v>0.282</v>
       </c>
       <c r="L8">
         <v>0.122</v>
       </c>
       <c r="M8">
-        <v>0.45600000000000002</v>
+        <v>0.456</v>
       </c>
       <c r="T8">
         <v>156.703</v>
       </c>
       <c r="U8">
-        <v>167.97900000000001</v>
+        <v>167.979</v>
       </c>
       <c r="W8">
-        <v>0.28299999999999997</v>
+        <v>0.283</v>
       </c>
       <c r="X8">
         <v>0.35</v>
       </c>
       <c r="Y8">
-        <v>1.0009999999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.001</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9">
         <v>2002</v>
       </c>
       <c r="B9">
-        <v>291.83699999999999</v>
+        <v>291.837</v>
       </c>
       <c r="C9">
-        <v>162.75800000000001</v>
+        <v>162.758</v>
       </c>
       <c r="E9">
         <v>0.245</v>
       </c>
       <c r="F9">
-        <v>0.28599999999999998</v>
+        <v>0.286</v>
       </c>
       <c r="G9">
         <v>1.03</v>
@@ -1475,7 +1444,7 @@
         <v>141.755</v>
       </c>
       <c r="K9">
-        <v>0.28899999999999998</v>
+        <v>0.289</v>
       </c>
       <c r="L9">
         <v>0.108</v>
@@ -1490,80 +1459,80 @@
         <v>183.761</v>
       </c>
       <c r="W9">
-        <v>0.20100000000000001</v>
+        <v>0.201</v>
       </c>
       <c r="X9">
-        <v>0.46400000000000002</v>
+        <v>0.464</v>
       </c>
       <c r="Y9">
         <v>1.171</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="10">
       <c r="A10">
         <v>2003</v>
       </c>
       <c r="B10">
-        <v>350.52100000000002</v>
+        <v>350.521</v>
       </c>
       <c r="C10">
         <v>182.458</v>
       </c>
       <c r="E10">
-        <v>0.20300000000000001</v>
+        <v>0.203</v>
       </c>
       <c r="F10">
-        <v>0.53700000000000003</v>
+        <v>0.537</v>
       </c>
       <c r="G10">
-        <v>0.98899999999999999</v>
+        <v>0.989</v>
       </c>
       <c r="H10">
-        <v>180.41300000000001</v>
+        <v>180.413</v>
       </c>
       <c r="I10">
-        <v>152.05199999999999</v>
+        <v>152.052</v>
       </c>
       <c r="K10">
-        <v>0.28399999999999997</v>
+        <v>0.284</v>
       </c>
       <c r="L10">
         <v>0.223</v>
       </c>
       <c r="M10">
-        <v>0.34599999999999997</v>
+        <v>0.346</v>
       </c>
       <c r="O10">
-        <v>211.11600000000001</v>
+        <v>211.116</v>
       </c>
       <c r="Q10">
-        <v>0.14599999999999999</v>
+        <v>0.146</v>
       </c>
       <c r="R10">
-        <v>0.85199999999999998</v>
+        <v>0.852</v>
       </c>
       <c r="T10">
         <v>170.108</v>
       </c>
       <c r="U10">
-        <v>184.20599999999999</v>
+        <v>184.206</v>
       </c>
       <c r="W10">
         <v>0.18</v>
       </c>
       <c r="X10">
-        <v>0.53700000000000003</v>
+        <v>0.537</v>
       </c>
       <c r="Y10">
-        <v>0.89400000000000002</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.894</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11">
         <v>2004</v>
       </c>
       <c r="B11">
-        <v>705.57799999999997</v>
+        <v>705.578</v>
       </c>
       <c r="C11">
         <v>170.828</v>
@@ -1572,43 +1541,43 @@
         <v>0.182</v>
       </c>
       <c r="F11">
-        <v>0.42699999999999999</v>
+        <v>0.427</v>
       </c>
       <c r="G11">
-        <v>0.92500000000000004</v>
+        <v>0.925</v>
       </c>
       <c r="H11">
-        <v>187.66800000000001</v>
+        <v>187.668</v>
       </c>
       <c r="I11">
-        <v>129.50700000000001</v>
+        <v>129.507</v>
       </c>
       <c r="K11">
-        <v>0.28999999999999998</v>
+        <v>0.29</v>
       </c>
       <c r="L11">
-        <v>6.2E-2</v>
+        <v>0.062</v>
       </c>
       <c r="M11">
-        <v>0.51700000000000002</v>
+        <v>0.517</v>
       </c>
       <c r="N11">
-        <v>340.08699999999999</v>
+        <v>340.087</v>
       </c>
       <c r="O11">
         <v>188.333</v>
       </c>
       <c r="Q11">
-        <v>7.2999999999999995E-2</v>
+        <v>0.073</v>
       </c>
       <c r="R11">
-        <v>0.55600000000000005</v>
+        <v>0.556</v>
       </c>
       <c r="S11">
-        <v>0.58899999999999997</v>
+        <v>0.589</v>
       </c>
       <c r="T11">
-        <v>177.82300000000001</v>
+        <v>177.823</v>
       </c>
       <c r="U11">
         <v>194.643</v>
@@ -1617,13 +1586,13 @@
         <v>0.183</v>
       </c>
       <c r="X11">
-        <v>0.66300000000000003</v>
+        <v>0.663</v>
       </c>
       <c r="Y11">
-        <v>0.68500000000000005</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.6850000000000001</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12">
         <v>2005</v>
       </c>
@@ -1631,43 +1600,43 @@
         <v>765.303</v>
       </c>
       <c r="C12">
-        <v>173.19499999999999</v>
+        <v>173.195</v>
       </c>
       <c r="E12">
-        <v>0.17399999999999999</v>
+        <v>0.174</v>
       </c>
       <c r="F12">
         <v>0.503</v>
       </c>
       <c r="G12">
-        <v>0.84899999999999998</v>
+        <v>0.849</v>
       </c>
       <c r="H12">
-        <v>93.025000000000006</v>
+        <v>93.02500000000001</v>
       </c>
       <c r="I12">
         <v>128.596</v>
       </c>
       <c r="K12">
-        <v>0.27800000000000002</v>
+        <v>0.278</v>
       </c>
       <c r="L12">
-        <v>4.2000000000000003E-2</v>
+        <v>0.042</v>
       </c>
       <c r="M12">
-        <v>0.65700000000000003</v>
+        <v>0.657</v>
       </c>
       <c r="N12">
-        <v>551.92100000000005</v>
+        <v>551.921</v>
       </c>
       <c r="O12">
-        <v>198.96600000000001</v>
+        <v>198.966</v>
       </c>
       <c r="Q12">
-        <v>8.3000000000000004E-2</v>
+        <v>0.083</v>
       </c>
       <c r="R12">
-        <v>0.82799999999999996</v>
+        <v>0.828</v>
       </c>
       <c r="S12">
         <v>0.51</v>
@@ -1682,13 +1651,13 @@
         <v>0.161</v>
       </c>
       <c r="X12">
-        <v>0.64100000000000001</v>
+        <v>0.641</v>
       </c>
       <c r="Y12">
-        <v>0.71199999999999997</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.712</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13">
         <v>2006</v>
       </c>
@@ -1696,55 +1665,55 @@
         <v>1489.942</v>
       </c>
       <c r="C13">
-        <v>158.93600000000001</v>
+        <v>158.936</v>
       </c>
       <c r="E13">
-        <v>0.19700000000000001</v>
+        <v>0.197</v>
       </c>
       <c r="F13">
-        <v>0.29699999999999999</v>
+        <v>0.297</v>
       </c>
       <c r="G13">
         <v>0.75</v>
       </c>
       <c r="H13">
-        <v>52.276000000000003</v>
+        <v>52.276</v>
       </c>
       <c r="I13">
         <v>129.673</v>
       </c>
       <c r="K13">
-        <v>0.24199999999999999</v>
+        <v>0.242</v>
       </c>
       <c r="L13">
         <v>0.04</v>
       </c>
       <c r="M13">
-        <v>0.72199999999999998</v>
+        <v>0.722</v>
       </c>
       <c r="N13">
         <v>1327.32</v>
       </c>
       <c r="S13">
-        <v>0.56999999999999995</v>
+        <v>0.57</v>
       </c>
       <c r="T13">
         <v>110.346</v>
       </c>
       <c r="U13">
-        <v>188.19900000000001</v>
+        <v>188.199</v>
       </c>
       <c r="W13">
         <v>0.152</v>
       </c>
       <c r="X13">
-        <v>0.55500000000000005</v>
+        <v>0.555</v>
       </c>
       <c r="Y13">
-        <v>0.65800000000000003</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.658</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14">
         <v>2007</v>
       </c>
@@ -1752,64 +1721,64 @@
         <v>3250.2</v>
       </c>
       <c r="C14">
-        <v>167.16200000000001</v>
+        <v>167.162</v>
       </c>
       <c r="E14">
-        <v>0.17699999999999999</v>
+        <v>0.177</v>
       </c>
       <c r="F14">
         <v>0.376</v>
       </c>
       <c r="G14">
-        <v>0.63600000000000001</v>
+        <v>0.636</v>
       </c>
       <c r="H14">
-        <v>42.075000000000003</v>
+        <v>42.075</v>
       </c>
       <c r="I14">
         <v>126.114</v>
       </c>
       <c r="K14">
-        <v>0.30099999999999999</v>
+        <v>0.301</v>
       </c>
       <c r="L14">
-        <v>5.2999999999999999E-2</v>
+        <v>0.053</v>
       </c>
       <c r="M14">
-        <v>0.90100000000000002</v>
+        <v>0.901</v>
       </c>
       <c r="N14">
         <v>3112.6</v>
       </c>
       <c r="O14">
-        <v>182.75899999999999</v>
+        <v>182.759</v>
       </c>
       <c r="Q14">
         <v>0.09</v>
       </c>
       <c r="R14">
-        <v>0.44800000000000001</v>
+        <v>0.448</v>
       </c>
       <c r="S14">
-        <v>0.47899999999999998</v>
+        <v>0.479</v>
       </c>
       <c r="T14">
-        <v>95.525999999999996</v>
+        <v>95.526</v>
       </c>
       <c r="U14">
         <v>192.613</v>
       </c>
       <c r="W14">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="X14">
         <v>0.626</v>
       </c>
       <c r="Y14">
-        <v>0.79400000000000004</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.794</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15">
         <v>2008</v>
       </c>
@@ -1817,60 +1786,60 @@
         <v>1837.23</v>
       </c>
       <c r="C15">
-        <v>158.69300000000001</v>
+        <v>158.693</v>
       </c>
       <c r="E15">
-        <v>0.23699999999999999</v>
+        <v>0.237</v>
       </c>
       <c r="F15">
         <v>0.376</v>
       </c>
       <c r="G15">
-        <v>0.59499999999999997</v>
+        <v>0.595</v>
       </c>
       <c r="H15">
-        <v>35.908000000000001</v>
+        <v>35.908</v>
       </c>
       <c r="I15">
         <v>125.514</v>
       </c>
       <c r="K15">
-        <v>0.32400000000000001</v>
+        <v>0.324</v>
       </c>
       <c r="L15">
         <v>0.111</v>
       </c>
       <c r="M15">
-        <v>1.1279999999999999</v>
+        <v>1.128</v>
       </c>
       <c r="N15">
         <v>1716.8</v>
       </c>
       <c r="S15">
-        <v>0.42899999999999999</v>
+        <v>0.429</v>
       </c>
       <c r="T15">
-        <v>84.522000000000006</v>
+        <v>84.52200000000001</v>
       </c>
       <c r="U15">
-        <v>191.87299999999999</v>
+        <v>191.873</v>
       </c>
       <c r="W15">
-        <v>0.14899999999999999</v>
+        <v>0.149</v>
       </c>
       <c r="X15">
-        <v>0.64200000000000002</v>
+        <v>0.642</v>
       </c>
       <c r="Y15">
-        <v>0.69</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16">
         <v>2009</v>
       </c>
       <c r="B16">
-        <v>1454.0039999999999</v>
+        <v>1454.004</v>
       </c>
       <c r="C16">
         <v>165.619</v>
@@ -1882,10 +1851,10 @@
         <v>0.378</v>
       </c>
       <c r="G16">
-        <v>0.57499999999999996</v>
+        <v>0.575</v>
       </c>
       <c r="H16">
-        <v>35.780999999999999</v>
+        <v>35.781</v>
       </c>
       <c r="I16">
         <v>139.739</v>
@@ -1894,7 +1863,7 @@
         <v>0.27</v>
       </c>
       <c r="L16">
-        <v>0.11600000000000001</v>
+        <v>0.116</v>
       </c>
       <c r="M16">
         <v>1.016</v>
@@ -1903,25 +1872,25 @@
         <v>1325.8</v>
       </c>
       <c r="S16">
-        <v>0.53500000000000003</v>
+        <v>0.535</v>
       </c>
       <c r="T16">
-        <v>92.423000000000002</v>
+        <v>92.423</v>
       </c>
       <c r="U16">
         <v>191.499</v>
       </c>
       <c r="W16">
-        <v>0.17499999999999999</v>
+        <v>0.175</v>
       </c>
       <c r="X16">
-        <v>0.63900000000000001</v>
+        <v>0.639</v>
       </c>
       <c r="Y16">
-        <v>0.56799999999999995</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.5679999999999999</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17">
         <v>2010</v>
       </c>
@@ -1932,22 +1901,22 @@
         <v>169.208</v>
       </c>
       <c r="E17">
-        <v>0.23899999999999999</v>
+        <v>0.239</v>
       </c>
       <c r="F17">
-        <v>0.41799999999999998</v>
+        <v>0.418</v>
       </c>
       <c r="G17">
-        <v>0.57199999999999995</v>
+        <v>0.572</v>
       </c>
       <c r="H17">
-        <v>36.563000000000002</v>
+        <v>36.563</v>
       </c>
       <c r="I17">
-        <v>136.79300000000001</v>
+        <v>136.793</v>
       </c>
       <c r="K17">
-        <v>0.29199999999999998</v>
+        <v>0.292</v>
       </c>
       <c r="L17">
         <v>0.11</v>
@@ -1959,25 +1928,25 @@
         <v>929.755</v>
       </c>
       <c r="S17">
-        <v>0.81899999999999995</v>
+        <v>0.819</v>
       </c>
       <c r="T17">
-        <v>117.79600000000001</v>
+        <v>117.796</v>
       </c>
       <c r="U17">
-        <v>201.62299999999999</v>
+        <v>201.623</v>
       </c>
       <c r="W17">
         <v>0.187</v>
       </c>
       <c r="X17">
-        <v>0.72599999999999998</v>
+        <v>0.726</v>
       </c>
       <c r="Y17">
-        <v>0.55500000000000005</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.555</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18">
         <v>2011</v>
       </c>
@@ -1988,10 +1957,10 @@
         <v>171.292</v>
       </c>
       <c r="E18">
-        <v>0.21299999999999999</v>
+        <v>0.213</v>
       </c>
       <c r="F18">
-        <v>0.39200000000000002</v>
+        <v>0.392</v>
       </c>
       <c r="G18">
         <v>0.622</v>
@@ -2006,7 +1975,7 @@
         <v>0.251</v>
       </c>
       <c r="L18">
-        <v>0.13900000000000001</v>
+        <v>0.139</v>
       </c>
       <c r="M18">
         <v>1.022</v>
@@ -2015,54 +1984,54 @@
         <v>1703.42</v>
       </c>
       <c r="S18">
-        <v>0.82799999999999996</v>
+        <v>0.828</v>
       </c>
       <c r="T18">
-        <v>99.444999999999993</v>
+        <v>99.44499999999999</v>
       </c>
       <c r="U18">
         <v>195.4</v>
       </c>
       <c r="W18">
-        <v>0.17599999999999999</v>
+        <v>0.176</v>
       </c>
       <c r="X18">
-        <v>0.64500000000000002</v>
+        <v>0.645</v>
       </c>
       <c r="Y18">
-        <v>0.82599999999999996</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.826</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19">
         <v>2012</v>
       </c>
       <c r="B19">
-        <v>2137.7130000000002</v>
+        <v>2137.713</v>
       </c>
       <c r="C19">
-        <v>158.97300000000001</v>
+        <v>158.973</v>
       </c>
       <c r="E19">
-        <v>0.20399999999999999</v>
+        <v>0.204</v>
       </c>
       <c r="F19">
-        <v>0.32200000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="G19">
-        <v>0.69099999999999995</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="H19">
-        <v>55.633000000000003</v>
+        <v>55.633</v>
       </c>
       <c r="I19">
         <v>125.884</v>
       </c>
       <c r="K19">
-        <v>0.26300000000000001</v>
+        <v>0.263</v>
       </c>
       <c r="L19">
-        <v>3.6999999999999998E-2</v>
+        <v>0.037</v>
       </c>
       <c r="M19">
         <v>1.544</v>
@@ -2077,57 +2046,57 @@
         <v>129.03</v>
       </c>
       <c r="U19">
-        <v>192.06200000000001</v>
+        <v>192.062</v>
       </c>
       <c r="W19">
-        <v>0.14499999999999999</v>
+        <v>0.145</v>
       </c>
       <c r="X19">
-        <v>0.60699999999999998</v>
+        <v>0.607</v>
       </c>
       <c r="Y19">
         <v>0.76</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="20">
       <c r="A20">
         <v>2013</v>
       </c>
       <c r="B20">
-        <v>1687.4829999999999</v>
+        <v>1687.483</v>
       </c>
       <c r="C20">
-        <v>155.57499999999999</v>
+        <v>155.575</v>
       </c>
       <c r="E20">
         <v>0.245</v>
       </c>
       <c r="F20">
-        <v>0.33300000000000002</v>
+        <v>0.333</v>
       </c>
       <c r="G20">
-        <v>0.75700000000000001</v>
+        <v>0.757</v>
       </c>
       <c r="H20">
-        <v>66.662999999999997</v>
+        <v>66.663</v>
       </c>
       <c r="I20">
-        <v>122.69799999999999</v>
+        <v>122.698</v>
       </c>
       <c r="K20">
-        <v>0.31900000000000001</v>
+        <v>0.319</v>
       </c>
       <c r="L20">
-        <v>7.3999999999999996E-2</v>
+        <v>0.074</v>
       </c>
       <c r="M20">
-        <v>1.6279999999999999</v>
+        <v>1.628</v>
       </c>
       <c r="N20">
         <v>1523.8</v>
       </c>
       <c r="S20">
-        <v>1.0680000000000001</v>
+        <v>1.068</v>
       </c>
       <c r="T20">
         <v>97.02</v>
@@ -2136,16 +2105,16 @@
         <v>188.452</v>
       </c>
       <c r="W20">
-        <v>0.17100000000000001</v>
+        <v>0.171</v>
       </c>
       <c r="X20">
-        <v>0.59299999999999997</v>
+        <v>0.593</v>
       </c>
       <c r="Y20">
         <v>0.76</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="21">
       <c r="A21">
         <v>2014</v>
       </c>
@@ -2153,7 +2122,7 @@
         <v>1573.498</v>
       </c>
       <c r="C21">
-        <v>159.90799999999999</v>
+        <v>159.908</v>
       </c>
       <c r="E21">
         <v>0.217</v>
@@ -2162,19 +2131,19 @@
         <v>0.318</v>
       </c>
       <c r="G21">
-        <v>0.83099999999999996</v>
+        <v>0.831</v>
       </c>
       <c r="H21">
-        <v>58.378999999999998</v>
+        <v>58.379</v>
       </c>
       <c r="I21">
-        <v>132.50200000000001</v>
+        <v>132.502</v>
       </c>
       <c r="K21">
-        <v>0.27400000000000002</v>
+        <v>0.274</v>
       </c>
       <c r="L21">
-        <v>4.2000000000000003E-2</v>
+        <v>0.042</v>
       </c>
       <c r="M21">
         <v>1.861</v>
@@ -2183,45 +2152,45 @@
         <v>1418.8</v>
       </c>
       <c r="S21">
-        <v>1.3720000000000001</v>
+        <v>1.372</v>
       </c>
       <c r="T21">
-        <v>96.319000000000003</v>
+        <v>96.319</v>
       </c>
       <c r="U21">
-        <v>187.31299999999999</v>
+        <v>187.313</v>
       </c>
       <c r="W21">
         <v>0.159</v>
       </c>
       <c r="X21">
-        <v>0.59499999999999997</v>
+        <v>0.595</v>
       </c>
       <c r="Y21">
-        <v>1.1919999999999999</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.192</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22">
         <v>2015</v>
       </c>
       <c r="B22">
-        <v>912.22199999999998</v>
+        <v>912.222</v>
       </c>
       <c r="C22">
-        <v>150.28800000000001</v>
+        <v>150.288</v>
       </c>
       <c r="E22">
-        <v>0.23300000000000001</v>
+        <v>0.233</v>
       </c>
       <c r="F22">
         <v>0.311</v>
       </c>
       <c r="G22">
-        <v>0.86699999999999999</v>
+        <v>0.867</v>
       </c>
       <c r="H22">
-        <v>42.084000000000003</v>
+        <v>42.084</v>
       </c>
       <c r="I22">
         <v>112.575</v>
@@ -2230,48 +2199,48 @@
         <v>0.32</v>
       </c>
       <c r="L22">
-        <v>3.7999999999999999E-2</v>
+        <v>0.038</v>
       </c>
       <c r="M22">
-        <v>1.9450000000000001</v>
+        <v>1.945</v>
       </c>
       <c r="N22">
-        <v>788.80499999999995</v>
+        <v>788.8049999999999</v>
       </c>
       <c r="T22">
-        <v>81.332999999999998</v>
+        <v>81.333</v>
       </c>
       <c r="U22">
         <v>188.001</v>
       </c>
       <c r="W22">
-        <v>0.14699999999999999</v>
+        <v>0.147</v>
       </c>
       <c r="X22">
-        <v>0.58399999999999996</v>
+        <v>0.584</v>
       </c>
       <c r="Y22">
-        <v>1.0980000000000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.098</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23">
         <v>2016</v>
       </c>
       <c r="B23">
-        <v>599.78899999999999</v>
+        <v>599.789</v>
       </c>
       <c r="C23">
-        <v>157.34200000000001</v>
+        <v>157.342</v>
       </c>
       <c r="E23">
-        <v>0.23300000000000001</v>
+        <v>0.233</v>
       </c>
       <c r="F23">
         <v>0.34</v>
       </c>
       <c r="G23">
-        <v>0.92200000000000004</v>
+        <v>0.922</v>
       </c>
       <c r="H23">
         <v>25.93</v>
@@ -2283,10 +2252,10 @@
         <v>0.31</v>
       </c>
       <c r="L23">
-        <v>9.1999999999999998E-2</v>
+        <v>0.092</v>
       </c>
       <c r="M23">
-        <v>1.3620000000000001</v>
+        <v>1.362</v>
       </c>
       <c r="N23">
         <v>502.51</v>
@@ -2295,22 +2264,22 @@
         <v>1.177</v>
       </c>
       <c r="T23">
-        <v>71.349999999999994</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="U23">
-        <v>189.03899999999999</v>
+        <v>189.039</v>
       </c>
       <c r="W23">
         <v>0.155</v>
       </c>
       <c r="X23">
-        <v>0.58799999999999997</v>
+        <v>0.588</v>
       </c>
       <c r="Y23">
         <v>1.175</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="24">
       <c r="A24">
         <v>2017</v>
       </c>
@@ -2318,63 +2287,63 @@
         <v>1088.893</v>
       </c>
       <c r="C24">
-        <v>142.90799999999999</v>
+        <v>142.908</v>
       </c>
       <c r="E24">
         <v>0.218</v>
       </c>
       <c r="F24">
-        <v>0.28899999999999998</v>
+        <v>0.289</v>
       </c>
       <c r="G24">
-        <v>0.98199999999999998</v>
+        <v>0.982</v>
       </c>
       <c r="H24">
         <v>30.276</v>
       </c>
       <c r="I24">
-        <v>98.391000000000005</v>
+        <v>98.39100000000001</v>
       </c>
       <c r="K24">
-        <v>0.29599999999999999</v>
+        <v>0.296</v>
       </c>
       <c r="L24">
-        <v>8.0000000000000002E-3</v>
+        <v>0.008</v>
       </c>
       <c r="M24">
-        <v>1.1759999999999999</v>
+        <v>1.176</v>
       </c>
       <c r="N24">
-        <v>983.88199999999995</v>
+        <v>983.8819999999999</v>
       </c>
       <c r="S24">
         <v>1.526</v>
       </c>
       <c r="T24">
-        <v>74.734999999999999</v>
+        <v>74.735</v>
       </c>
       <c r="U24">
-        <v>187.42400000000001</v>
+        <v>187.424</v>
       </c>
       <c r="W24">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="X24">
-        <v>0.56999999999999995</v>
+        <v>0.57</v>
       </c>
       <c r="Y24">
-        <v>1.3089999999999999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.309</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25">
         <v>2018</v>
       </c>
       <c r="B25">
-        <v>1373.6610000000001</v>
+        <v>1373.661</v>
       </c>
       <c r="C25">
-        <v>140.94399999999999</v>
+        <v>140.944</v>
       </c>
       <c r="E25">
         <v>0.307</v>
@@ -2386,48 +2355,48 @@
         <v>1.087</v>
       </c>
       <c r="H25">
-        <v>42.966999999999999</v>
+        <v>42.967</v>
       </c>
       <c r="I25">
-        <v>98.519000000000005</v>
+        <v>98.51900000000001</v>
       </c>
       <c r="K25">
-        <v>0.46899999999999997</v>
+        <v>0.469</v>
       </c>
       <c r="L25">
-        <v>8.7999999999999995E-2</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="M25">
-        <v>1.4219999999999999</v>
+        <v>1.422</v>
       </c>
       <c r="N25">
         <v>1255.27</v>
       </c>
       <c r="S25">
-        <v>2.3879999999999999</v>
+        <v>2.388</v>
       </c>
       <c r="T25">
-        <v>75.424999999999997</v>
+        <v>75.425</v>
       </c>
       <c r="U25">
-        <v>183.36799999999999</v>
+        <v>183.368</v>
       </c>
       <c r="W25">
-        <v>0.14399999999999999</v>
+        <v>0.144</v>
       </c>
       <c r="X25">
-        <v>0.52500000000000002</v>
+        <v>0.525</v>
       </c>
       <c r="Y25">
-        <v>1.2490000000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.249</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26">
         <v>2019</v>
       </c>
       <c r="B26">
-        <v>1521.1210000000001</v>
+        <v>1521.121</v>
       </c>
       <c r="C26">
         <v>156.03</v>
@@ -2436,7 +2405,7 @@
         <v>0.25</v>
       </c>
       <c r="F26">
-        <v>0.38300000000000001</v>
+        <v>0.383</v>
       </c>
       <c r="G26">
         <v>1.234</v>
@@ -2448,10 +2417,10 @@
         <v>119.379</v>
       </c>
       <c r="K26">
-        <v>0.36599999999999999</v>
+        <v>0.366</v>
       </c>
       <c r="L26">
-        <v>8.5999999999999993E-2</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="M26">
         <v>1.401</v>
@@ -2460,16 +2429,16 @@
         <v>1422.63</v>
       </c>
       <c r="S26">
-        <v>1.6259999999999999</v>
+        <v>1.626</v>
       </c>
       <c r="T26">
-        <v>88.036000000000001</v>
+        <v>88.036</v>
       </c>
       <c r="U26">
-        <v>192.68100000000001</v>
+        <v>192.681</v>
       </c>
       <c r="W26">
-        <v>0.13400000000000001</v>
+        <v>0.134</v>
       </c>
       <c r="X26">
         <v>0.68</v>
@@ -2478,21 +2447,21 @@
         <v>1.159</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="27">
       <c r="A27">
         <v>2020</v>
       </c>
       <c r="B27">
-        <v>95.995000000000005</v>
+        <v>95.995</v>
       </c>
       <c r="C27">
-        <v>183.59100000000001</v>
+        <v>183.591</v>
       </c>
       <c r="E27">
         <v>0.13</v>
       </c>
       <c r="F27">
-        <v>0.61499999999999999</v>
+        <v>0.615</v>
       </c>
       <c r="G27">
         <v>1.38</v>
@@ -2501,16 +2470,16 @@
         <v>22.83</v>
       </c>
       <c r="T27">
-        <v>73.165000000000006</v>
+        <v>73.16500000000001</v>
       </c>
       <c r="U27">
-        <v>183.59100000000001</v>
+        <v>183.591</v>
       </c>
       <c r="W27">
         <v>0.13</v>
       </c>
       <c r="X27">
-        <v>0.61499999999999999</v>
+        <v>0.615</v>
       </c>
     </row>
   </sheetData>

--- a/Indicator_4/Real_data/Blue_Shark_SWPac.xlsx
+++ b/Indicator_4/Real_data/Blue_Shark_SWPac.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Parameters" sheetId="1" r:id="rId1"/>
     <sheet name="Time_series" sheetId="2" r:id="rId2"/>
+    <sheet name="B_BMSY" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.552</t>
+          <t>326.07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -498,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>326.07</t>
+          <t>0.552</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1093,15 +1094,6 @@
       <c r="M2">
         <v>0.416</v>
       </c>
-      <c r="O2">
-        <v>201.915</v>
-      </c>
-      <c r="Q2">
-        <v>0.151</v>
-      </c>
-      <c r="R2">
-        <v>0.638</v>
-      </c>
       <c r="T2">
         <v>69.161</v>
       </c>
@@ -1502,15 +1494,6 @@
       <c r="M10">
         <v>0.346</v>
       </c>
-      <c r="O10">
-        <v>211.116</v>
-      </c>
-      <c r="Q10">
-        <v>0.146</v>
-      </c>
-      <c r="R10">
-        <v>0.852</v>
-      </c>
       <c r="T10">
         <v>170.108</v>
       </c>
@@ -1561,21 +1544,6 @@
       <c r="M11">
         <v>0.517</v>
       </c>
-      <c r="N11">
-        <v>340.087</v>
-      </c>
-      <c r="O11">
-        <v>188.333</v>
-      </c>
-      <c r="Q11">
-        <v>0.073</v>
-      </c>
-      <c r="R11">
-        <v>0.556</v>
-      </c>
-      <c r="S11">
-        <v>0.589</v>
-      </c>
       <c r="T11">
         <v>177.823</v>
       </c>
@@ -1626,21 +1594,6 @@
       <c r="M12">
         <v>0.657</v>
       </c>
-      <c r="N12">
-        <v>551.921</v>
-      </c>
-      <c r="O12">
-        <v>198.966</v>
-      </c>
-      <c r="Q12">
-        <v>0.083</v>
-      </c>
-      <c r="R12">
-        <v>0.828</v>
-      </c>
-      <c r="S12">
-        <v>0.51</v>
-      </c>
       <c r="T12">
         <v>120.357</v>
       </c>
@@ -1691,12 +1644,6 @@
       <c r="M13">
         <v>0.722</v>
       </c>
-      <c r="N13">
-        <v>1327.32</v>
-      </c>
-      <c r="S13">
-        <v>0.57</v>
-      </c>
       <c r="T13">
         <v>110.346</v>
       </c>
@@ -1747,21 +1694,6 @@
       <c r="M14">
         <v>0.901</v>
       </c>
-      <c r="N14">
-        <v>3112.6</v>
-      </c>
-      <c r="O14">
-        <v>182.759</v>
-      </c>
-      <c r="Q14">
-        <v>0.09</v>
-      </c>
-      <c r="R14">
-        <v>0.448</v>
-      </c>
-      <c r="S14">
-        <v>0.479</v>
-      </c>
       <c r="T14">
         <v>95.526</v>
       </c>
@@ -1812,12 +1744,6 @@
       <c r="M15">
         <v>1.128</v>
       </c>
-      <c r="N15">
-        <v>1716.8</v>
-      </c>
-      <c r="S15">
-        <v>0.429</v>
-      </c>
       <c r="T15">
         <v>84.52200000000001</v>
       </c>
@@ -1868,12 +1794,6 @@
       <c r="M16">
         <v>1.016</v>
       </c>
-      <c r="N16">
-        <v>1325.8</v>
-      </c>
-      <c r="S16">
-        <v>0.535</v>
-      </c>
       <c r="T16">
         <v>92.423</v>
       </c>
@@ -1924,12 +1844,6 @@
       <c r="M17">
         <v>1.052</v>
       </c>
-      <c r="N17">
-        <v>929.755</v>
-      </c>
-      <c r="S17">
-        <v>0.819</v>
-      </c>
       <c r="T17">
         <v>117.796</v>
       </c>
@@ -1980,12 +1894,6 @@
       <c r="M18">
         <v>1.022</v>
       </c>
-      <c r="N18">
-        <v>1703.42</v>
-      </c>
-      <c r="S18">
-        <v>0.828</v>
-      </c>
       <c r="T18">
         <v>99.44499999999999</v>
       </c>
@@ -2036,12 +1944,6 @@
       <c r="M19">
         <v>1.544</v>
       </c>
-      <c r="N19">
-        <v>1953.05</v>
-      </c>
-      <c r="S19">
-        <v>1.083</v>
-      </c>
       <c r="T19">
         <v>129.03</v>
       </c>
@@ -2092,12 +1994,6 @@
       <c r="M20">
         <v>1.628</v>
       </c>
-      <c r="N20">
-        <v>1523.8</v>
-      </c>
-      <c r="S20">
-        <v>1.068</v>
-      </c>
       <c r="T20">
         <v>97.02</v>
       </c>
@@ -2148,12 +2044,6 @@
       <c r="M21">
         <v>1.861</v>
       </c>
-      <c r="N21">
-        <v>1418.8</v>
-      </c>
-      <c r="S21">
-        <v>1.372</v>
-      </c>
       <c r="T21">
         <v>96.319</v>
       </c>
@@ -2204,9 +2094,6 @@
       <c r="M22">
         <v>1.945</v>
       </c>
-      <c r="N22">
-        <v>788.8049999999999</v>
-      </c>
       <c r="T22">
         <v>81.333</v>
       </c>
@@ -2257,12 +2144,6 @@
       <c r="M23">
         <v>1.362</v>
       </c>
-      <c r="N23">
-        <v>502.51</v>
-      </c>
-      <c r="S23">
-        <v>1.177</v>
-      </c>
       <c r="T23">
         <v>71.34999999999999</v>
       </c>
@@ -2313,12 +2194,6 @@
       <c r="M24">
         <v>1.176</v>
       </c>
-      <c r="N24">
-        <v>983.8819999999999</v>
-      </c>
-      <c r="S24">
-        <v>1.526</v>
-      </c>
       <c r="T24">
         <v>74.735</v>
       </c>
@@ -2369,12 +2244,6 @@
       <c r="M25">
         <v>1.422</v>
       </c>
-      <c r="N25">
-        <v>1255.27</v>
-      </c>
-      <c r="S25">
-        <v>2.388</v>
-      </c>
       <c r="T25">
         <v>75.425</v>
       </c>
@@ -2425,12 +2294,6 @@
       <c r="M26">
         <v>1.401</v>
       </c>
-      <c r="N26">
-        <v>1422.63</v>
-      </c>
-      <c r="S26">
-        <v>1.626</v>
-      </c>
       <c r="T26">
         <v>88.036</v>
       </c>
@@ -2480,6 +2343,371 @@
       </c>
       <c r="X27">
         <v>0.615</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C27"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>StDev</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SSB_1995</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>1.506716915091431</v>
+      </c>
+      <c r="C2">
+        <v>0.07883540326349597</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SSB_1996</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>1.524257460200662</v>
+      </c>
+      <c r="C3">
+        <v>0.08394632434098659</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SSB_1997</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>1.471287798184295</v>
+      </c>
+      <c r="C4">
+        <v>0.08790020583292729</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SSB_1998</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>1.393598297652311</v>
+      </c>
+      <c r="C5">
+        <v>0.09138852705161732</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SSB_1999</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>1.27253472809172</v>
+      </c>
+      <c r="C6">
+        <v>0.09341931249813556</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SSB_2000</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>1.15182912883948</v>
+      </c>
+      <c r="C7">
+        <v>0.09434963755506279</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SSB_2001</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>1.105969154891764</v>
+      </c>
+      <c r="C8">
+        <v>0.09328905108037426</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SSB_2002</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>1.035120864697167</v>
+      </c>
+      <c r="C9">
+        <v>0.08945658118468285</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SSB_2003</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>0.9498791850209312</v>
+      </c>
+      <c r="C10">
+        <v>0.08422146429743355</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SSB_2004</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>0.838818896854833</v>
+      </c>
+      <c r="C11">
+        <v>0.07758956715423547</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SSB_2005</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>0.7116429842791372</v>
+      </c>
+      <c r="C12">
+        <v>0.0710764962661708</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SSB_2006</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>0.665313671482693</v>
+      </c>
+      <c r="C13">
+        <v>0.06752463531774837</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SSB_2007</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>0.6437061859258008</v>
+      </c>
+      <c r="C14">
+        <v>0.06579882068670638</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SSB_2008</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>0.6404208139847067</v>
+      </c>
+      <c r="C15">
+        <v>0.06612606521025784</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SSB_2009</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>0.6959599073254646</v>
+      </c>
+      <c r="C16">
+        <v>0.06870951703839231</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SSB_2010</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>0.7733699921445404</v>
+      </c>
+      <c r="C17">
+        <v>0.07307526325733092</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SSB_2011</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>0.8473763759483726</v>
+      </c>
+      <c r="C18">
+        <v>0.07892032177553272</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SSB_2012</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>0.9298338421152067</v>
+      </c>
+      <c r="C19">
+        <v>0.08625374128690325</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SSB_2013</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>0.9703123290940366</v>
+      </c>
+      <c r="C20">
+        <v>0.09406882973540028</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SSB_2014</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>1.03112352958724</v>
+      </c>
+      <c r="C21">
+        <v>0.1022959817832887</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SSB_2015</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>1.098610876331202</v>
+      </c>
+      <c r="C22">
+        <v>0.1105004623783149</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SSB_2016</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>1.216542205693717</v>
+      </c>
+      <c r="C23">
+        <v>0.1198057016715224</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SSB_2017</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>1.380790915509064</v>
+      </c>
+      <c r="C24">
+        <v>0.1310608847832788</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SSB_2018</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>1.543766842005827</v>
+      </c>
+      <c r="C25">
+        <v>0.1437012141159625</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SSB_2019</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>1.679258603716925</v>
+      </c>
+      <c r="C26">
+        <v>0.1563793292034166</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SSB_2020</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>1.774588085554904</v>
+      </c>
+      <c r="C27">
+        <v>0.1681048455258683</v>
       </c>
     </row>
   </sheetData>
